--- a/docs/data/raw/2026-07-04_ST.xlsx
+++ b/docs/data/raw/2026-07-04_ST.xlsx
@@ -1151,7 +1151,7 @@
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="14">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="26">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="37">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="38">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="44">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="45">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="58">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="59">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="70">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="71">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="82">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="83">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="88">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="96">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="97">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="102">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="108">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="109">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="112">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="114">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="120">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="n">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="121">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="123">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="124">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="125">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="126">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129">
@@ -8250,10 +8250,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -8304,10 +8304,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -8358,10 +8358,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
         <v>12</v>
@@ -8412,10 +8412,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>12</v>
@@ -8466,10 +8466,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -8520,10 +8520,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -8574,10 +8574,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
@@ -8628,10 +8628,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -8682,10 +8682,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -8736,10 +8736,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -8980,10 +8980,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -9034,10 +9034,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -9088,10 +9088,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
         <v>12</v>
@@ -9142,10 +9142,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>12</v>
@@ -9196,10 +9196,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -9250,10 +9250,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -9304,10 +9304,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
@@ -9358,10 +9358,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -9412,10 +9412,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -9466,10 +9466,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -9710,10 +9710,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -9764,10 +9764,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -9818,10 +9818,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
@@ -9872,10 +9872,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -9926,10 +9926,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -9980,10 +9980,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -10034,10 +10034,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
@@ -10088,10 +10088,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
         <v>14</v>
@@ -10142,10 +10142,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
         <v>14</v>
@@ -10196,10 +10196,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="M11" t="n">
         <v>14</v>
@@ -18550,14 +18550,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18571,14 +18571,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18592,14 +18592,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18613,14 +18613,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18634,14 +18634,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18655,14 +18655,14 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18676,14 +18676,14 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18697,14 +18697,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18718,14 +18718,14 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18739,14 +18739,14 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18760,14 +18760,14 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18781,14 +18781,14 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18802,14 +18802,14 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18823,14 +18823,14 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18844,14 +18844,14 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18865,14 +18865,14 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18886,14 +18886,14 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D18" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18907,14 +18907,14 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18928,14 +18928,14 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18949,14 +18949,14 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18970,14 +18970,14 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -18991,14 +18991,14 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="D23" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19012,14 +19012,14 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19033,14 +19033,14 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19054,14 +19054,14 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19075,14 +19075,14 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19096,14 +19096,14 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D28" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19117,14 +19117,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19138,14 +19138,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19159,14 +19159,14 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D31" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19180,14 +19180,14 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19201,14 +19201,14 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="D33" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19222,14 +19222,14 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D34" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19243,14 +19243,14 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D35" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19264,14 +19264,14 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D36" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19285,14 +19285,14 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="D37" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19306,14 +19306,14 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D38" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19327,14 +19327,14 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="D39" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19348,14 +19348,14 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D40" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19369,14 +19369,14 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D41" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19390,14 +19390,14 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19411,14 +19411,14 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="D43" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19432,14 +19432,14 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D44" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19453,14 +19453,14 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19474,14 +19474,14 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D46" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19495,14 +19495,14 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="D47" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19516,14 +19516,14 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D48" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19537,14 +19537,14 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="D49" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19558,14 +19558,14 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D50" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19579,14 +19579,14 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D51" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19600,14 +19600,14 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19621,14 +19621,14 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="D53" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19642,14 +19642,14 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D54" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19663,14 +19663,14 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19684,14 +19684,14 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D56" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19705,14 +19705,14 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="D57" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19726,14 +19726,14 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D58" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19747,14 +19747,14 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19768,14 +19768,14 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D60" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19789,14 +19789,14 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D61" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19810,14 +19810,14 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19831,14 +19831,14 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="D63" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19852,14 +19852,14 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D64" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19873,14 +19873,14 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D65" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19894,14 +19894,14 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D66" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19915,14 +19915,14 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="D67" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19936,14 +19936,14 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D68" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19957,14 +19957,14 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="D69" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19978,14 +19978,14 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D70" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -19999,14 +19999,14 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D71" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20020,14 +20020,14 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20041,14 +20041,14 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="D73" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20062,14 +20062,14 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D74" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20083,14 +20083,14 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D75" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20104,14 +20104,14 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D76" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20125,14 +20125,14 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="D77" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20146,14 +20146,14 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D78" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20167,14 +20167,14 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="D79" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20188,14 +20188,14 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D80" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20209,14 +20209,14 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D81" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20230,14 +20230,14 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20251,14 +20251,14 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="D83" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20272,14 +20272,14 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D84" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20293,14 +20293,14 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D85" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20314,14 +20314,14 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D86" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20335,14 +20335,14 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="D87" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20356,14 +20356,14 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D88" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20377,14 +20377,14 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="D89" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20398,14 +20398,14 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D90" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20419,14 +20419,14 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D91" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20440,14 +20440,14 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20461,14 +20461,14 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
       <c r="D93" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20482,14 +20482,14 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D94" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20503,14 +20503,14 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D95" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20524,14 +20524,14 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D96" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20545,14 +20545,14 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="D97" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20566,14 +20566,14 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D98" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20587,14 +20587,14 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="D99" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20608,14 +20608,14 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D100" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20629,14 +20629,14 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D101" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20650,14 +20650,14 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20671,14 +20671,14 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
       <c r="D103" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20692,14 +20692,14 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D104" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20713,14 +20713,14 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D105" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20734,14 +20734,14 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D106" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20755,14 +20755,14 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="D107" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20776,14 +20776,14 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D108" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20797,14 +20797,14 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="D109" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20818,14 +20818,14 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D110" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -20839,14 +20839,14 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D111" t="n">
-        <v>9.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>12:48:34</t>
+          <t>12:40:16</t>
         </is>
       </c>
     </row>
@@ -21569,10 +21569,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -21623,10 +21623,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -21677,10 +21677,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
         <v>12</v>
@@ -21731,10 +21731,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>12</v>
@@ -21785,10 +21785,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -21839,10 +21839,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -21893,10 +21893,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
@@ -21947,10 +21947,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -22001,10 +22001,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -22055,10 +22055,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -22299,10 +22299,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -22353,10 +22353,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -22407,10 +22407,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
         <v>12</v>
@@ -22461,10 +22461,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>12</v>
@@ -22515,10 +22515,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -22569,10 +22569,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -22623,10 +22623,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
@@ -22677,10 +22677,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -22731,10 +22731,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -22785,10 +22785,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -23029,10 +23029,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>7</v>
@@ -23083,10 +23083,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>7</v>
@@ -23137,10 +23137,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
         <v>7</v>
@@ -23191,10 +23191,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>7</v>
@@ -23245,10 +23245,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M6" t="n">
         <v>7</v>
@@ -23299,10 +23299,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M7" t="n">
         <v>7</v>
@@ -23353,10 +23353,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="M8" t="n">
         <v>7</v>
@@ -23493,10 +23493,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -23547,10 +23547,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -23601,10 +23601,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
@@ -23655,10 +23655,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -23709,10 +23709,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -23763,10 +23763,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -23817,10 +23817,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
@@ -23871,10 +23871,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
         <v>14</v>
@@ -23925,10 +23925,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
         <v>14</v>
@@ -23979,10 +23979,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="M11" t="n">
         <v>14</v>
@@ -24327,10 +24327,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -24381,10 +24381,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -24435,10 +24435,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
         <v>12</v>
@@ -24489,10 +24489,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>12</v>
@@ -24543,10 +24543,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -24597,10 +24597,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -24651,10 +24651,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
@@ -24705,10 +24705,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -24759,10 +24759,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -24813,10 +24813,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -25057,10 +25057,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -25111,10 +25111,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -25165,10 +25165,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
         <v>12</v>
@@ -25219,10 +25219,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>12</v>
@@ -25273,10 +25273,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -25327,10 +25327,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -25381,10 +25381,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
@@ -25435,10 +25435,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -25489,10 +25489,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -25543,10 +25543,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -25787,10 +25787,10 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>14</v>
@@ -25841,10 +25841,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -25895,10 +25895,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
         <v>14</v>
@@ -25949,10 +25949,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -26003,10 +26003,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M6" t="n">
         <v>14</v>
@@ -26057,10 +26057,10 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -26111,10 +26111,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
@@ -26165,10 +26165,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
         <v>14</v>
@@ -26219,10 +26219,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
         <v>14</v>
@@ -26273,10 +26273,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="M11" t="n">
         <v>14</v>
